--- a/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
+++ b/projects/project-3/assignment/src/data/bfo-core-ies-structural-matches-with-defs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,3996 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000011</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>spatiotemporal region</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000011 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000011</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatiotemporal region is an occurrent that is an occurrent part of spacetime</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000011</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>spatiotemporal region</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000011 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000011</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatiotemporal region is an occurrent that is an occurrent part of spacetime</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000011</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>spatiotemporal region</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000011 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000011</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatiotemporal region is an occurrent that is an occurrent part of spacetime</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000011</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>spatiotemporal region</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000011 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000011</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatiotemporal region is an occurrent that is an occurrent part of spacetime</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000028</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>three-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>(Elucidation) A three-dimensional spatial region is a whole consisting of a spatial volume together with zero or more spatial volumes which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000028</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>three-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>(Elucidation) A three-dimensional spatial region is a whole consisting of a spatial volume together with zero or more spatial volumes which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000028</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>three-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>(Elucidation) A three-dimensional spatial region is a whole consisting of a spatial volume together with zero or more spatial volumes which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000028</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>three-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>(Elucidation) A three-dimensional spatial region is a whole consisting of a spatial volume together with zero or more spatial volumes which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>two-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000009 OR ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>(Elucidation) A two-dimensional spatial region is a spatial region that is a whole consisting of a surface together with zero or more surfaces which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000009</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>two-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000009 OR ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>(Elucidation) A two-dimensional spatial region is a spatial region that is a whole consisting of a surface together with zero or more surfaces which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000009</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>two-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000009 OR ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>(Elucidation) A two-dimensional spatial region is a spatial region that is a whole consisting of a surface together with zero or more surfaces which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000009</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>two-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000009 OR ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>(Elucidation) A two-dimensional spatial region is a spatial region that is a whole consisting of a surface together with zero or more surfaces which may have spatial regions of lower dimension as parts</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000004</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000002 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000004</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>b is an independent continuant =Def b is a continuant &amp; there is no c such that b specifically depends on c or b generically depends on c</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000004</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000002 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000004</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>b is an independent continuant =Def b is a continuant &amp; there is no c such that b specifically depends on c or b generically depends on c</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000002 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000004</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>b is an independent continuant =Def b is a continuant &amp; there is no c such that b specifically depends on c or b generically depends on c</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000002 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000004</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>b is an independent continuant =Def b is a continuant &amp; there is no c such that b specifically depends on c or b generically depends on c</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000040</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000004 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000040 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000040 OR ns1:BFO_0000140)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>(Elucidation) A material entity is an independent continuant that at all times at which it exists has some portion of matter as continuant part</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000040</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000004 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000040 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000040 OR ns1:BFO_0000140)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>(Elucidation) A material entity is an independent continuant that at all times at which it exists has some portion of matter as continuant part</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000040</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000004 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000040 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000040 OR ns1:BFO_0000140)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>(Elucidation) A material entity is an independent continuant that at all times at which it exists has some portion of matter as continuant part</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000040</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000004 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000040 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000040 OR ns1:BFO_0000140)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>(Elucidation) A material entity is an independent continuant that at all times at which it exists has some portion of matter as continuant part</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000029</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only (ns1:BFO_0000029 OR ns1:BFO_0000040) | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000140) | SubClassOf: ns1:BFO_0000210 only ns1:BFO_0000028</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>(Elucidation) A site is a three-dimensional immaterial entity whose boundaries either (partially or wholly) coincide with the boundaries of one or more material entities or have locations determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000029</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only (ns1:BFO_0000029 OR ns1:BFO_0000040) | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000140) | SubClassOf: ns1:BFO_0000210 only ns1:BFO_0000028</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>(Elucidation) A site is a three-dimensional immaterial entity whose boundaries either (partially or wholly) coincide with the boundaries of one or more material entities or have locations determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000029</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only (ns1:BFO_0000029 OR ns1:BFO_0000040) | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000140) | SubClassOf: ns1:BFO_0000210 only ns1:BFO_0000028</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>(Elucidation) A site is a three-dimensional immaterial entity whose boundaries either (partially or wholly) coincide with the boundaries of one or more material entities or have locations determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000029</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only (ns1:BFO_0000029 OR ns1:BFO_0000040) | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000029 OR ns1:BFO_0000140) | SubClassOf: ns1:BFO_0000210 only ns1:BFO_0000028</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>(Elucidation) A site is a three-dimensional immaterial entity whose boundaries either (partially or wholly) coincide with the boundaries of one or more material entities or have locations determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000015</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000015 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000015</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>(Elucidation) p is a process means p is an occurrent that has some temporal proper part and for some time t, p has some material entity as participant</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000015</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000015 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000015</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>(Elucidation) p is a process means p is an occurrent that has some temporal proper part and for some time t, p has some material entity as participant</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000015</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000015 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000015</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>(Elucidation) p is a process means p is an occurrent that has some temporal proper part and for some time t, p has some material entity as participant</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000015</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>R:only×3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000015 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000015</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>(Elucidation) p is a process means p is an occurrent that has some temporal proper part and for some time t, p has some material entity as participant</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000018</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>zero-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000018</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional spatial region is one or a collection of more than one spatially disjoint points in space</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000018</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>zero-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000018</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional spatial region is one or a collection of more than one spatially disjoint points in space</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000018</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>zero-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000018</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional spatial region is one or a collection of more than one spatially disjoint points in space</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000018</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>zero-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000018</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional spatial region is one or a collection of more than one spatially disjoint points in space</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000008</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000132 only ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>(Elucidation) A temporal region is an occurrent over which processes can unfold</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000140</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>continuant fiat boundary</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000124 only ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant fiat boundary b is an immaterial entity that is of zero, one or two dimensions &amp; such that there is no time t when b has a spatial region as continuant part &amp; whose location is determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000140</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>continuant fiat boundary</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000124 only ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant fiat boundary b is an immaterial entity that is of zero, one or two dimensions &amp; such that there is no time t when b has a spatial region as continuant part &amp; whose location is determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000140</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>continuant fiat boundary</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000124 only ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant fiat boundary b is an immaterial entity that is of zero, one or two dimensions &amp; such that there is no time t when b has a spatial region as continuant part &amp; whose location is determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000140</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>continuant fiat boundary</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000124 only ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant fiat boundary b is an immaterial entity that is of zero, one or two dimensions &amp; such that there is no time t when b has a spatial region as continuant part &amp; whose location is determined in relation to some material entity</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only (ns1:BFO_0000038 OR ns1:BFO_0000148) | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000038</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional temporal region is a temporal region that is a whole that has a temporal interval and zero or more temporal intervals and temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only (ns1:BFO_0000038 OR ns1:BFO_0000148) | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000038</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional temporal region is a temporal region that is a whole that has a temporal interval and zero or more temporal intervals and temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only (ns1:BFO_0000038 OR ns1:BFO_0000148) | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000038</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional temporal region is a temporal region that is a whole that has a temporal interval and zero or more temporal intervals and temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>R:only×2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only (ns1:BFO_0000038 OR ns1:BFO_0000148) | SubClassOf: ns1:BFO_0000139 only ns1:BFO_0000038</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional temporal region is a temporal region that is a whole that has a temporal interval and zero or more temporal intervals and temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000148</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>zero-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000148</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional temporal region is a temporal region that is a whole consisting of one or more separated temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000148</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>zero-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000148</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional temporal region is a temporal region that is a whole consisting of one or more separated temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000148</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>zero-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000148</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional temporal region is a temporal region that is a whole consisting of one or more separated temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000148</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>zero-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000008 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000148</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>(Elucidation) A zero-dimensional temporal region is a temporal region that is a whole consisting of one or more separated temporal instants as parts</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000006</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>spatial region</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatial region is a continuant entity that is a continuant part of the spatial projection of a portion of spacetime at a given time</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000006</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>spatial region</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatial region is a continuant entity that is a continuant part of the spatial projection of a portion of spacetime at a given time</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000006</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>spatial region</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatial region is a continuant entity that is a continuant part of the spatial projection of a portion of spacetime at a given time</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000006</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>spatial region</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000141 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000006</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>(Elucidation) A spatial region is a continuant entity that is a continuant part of the spatial projection of a portion of spacetime at a given time</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000147</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>fiat point</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000147</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat point is a zero-dimensional continuant fiat boundary that consists of a single point</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000147</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>fiat point</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000147</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat point is a zero-dimensional continuant fiat boundary that consists of a single point</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000147</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>fiat point</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000147</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat point is a zero-dimensional continuant fiat boundary that consists of a single point</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000147</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>fiat point</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000147</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat point is a zero-dimensional continuant fiat boundary that consists of a single point</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>one-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional spatial region is a whole consisting of a line together with zero or more lines which may have points as parts</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>one-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional spatial region is a whole consisting of a line together with zero or more lines which may have points as parts</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>one-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional spatial region is a whole consisting of a line together with zero or more lines which may have points as parts</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>one-dimensional spatial region</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000006 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000018 OR ns1:BFO_0000026)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>(Elucidation) A one-dimensional spatial region is a whole consisting of a line together with zero or more lines which may have points as parts</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000002</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000001 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000002</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant is an entity that persists, endures, or continues to exist through time while maintaining its identity</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000002</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000001 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000002</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant is an entity that persists, endures, or continues to exist through time while maintaining its identity</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000002</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000001 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000002</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant is an entity that persists, endures, or continues to exist through time while maintaining its identity</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000002</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000001 | SubClassOf: ns1:BFO_0000176 only ns1:BFO_0000002</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>(Elucidation) A continuant is an entity that persists, endures, or continues to exist through time while maintaining its identity</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000142</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>fiat line</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000142 OR ns1:BFO_0000147)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat line is a one-dimensional continuant fiat boundary that is continuous</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000142</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>fiat line</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000142 OR ns1:BFO_0000147)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat line is a one-dimensional continuant fiat boundary that is continuous</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000142</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>fiat line</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000142 OR ns1:BFO_0000147)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat line is a one-dimensional continuant fiat boundary that is continuous</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000142</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>fiat line</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only (ns1:BFO_0000142 OR ns1:BFO_0000147)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat line is a one-dimensional continuant fiat boundary that is continuous</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000035</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>process boundary</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>R:only×4</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000132 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000139 only (ns1:BFO_0000015 OR ns1:BFO_0000035)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>p is a process boundary =Def p is a temporal part of a process &amp; p has no proper temporal parts</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000035</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>process boundary</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>R:only×4</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000132 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000139 only (ns1:BFO_0000015 OR ns1:BFO_0000035)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>p is a process boundary =Def p is a temporal part of a process &amp; p has no proper temporal parts</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000035</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>process boundary</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>R:only×4</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000132 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000139 only (ns1:BFO_0000015 OR ns1:BFO_0000035)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>p is a process boundary =Def p is a temporal part of a process &amp; p has no proper temporal parts</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000035</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>process boundary</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>R:only×4</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000003 | SubClassOf: ns1:BFO_0000117 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000121 only ns1:BFO_0000035 | SubClassOf: ns1:BFO_0000132 only (ns1:BFO_0000015 OR ns1:BFO_0000035) | SubClassOf: ns1:BFO_0000139 only (ns1:BFO_0000015 OR ns1:BFO_0000035)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>p is a process boundary =Def p is a temporal part of a process &amp; p has no proper temporal parts</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000146</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>fiat surface</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#AccountHolder</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ResponsibleActorState | SubClassOf: ies:holdsAccount only ies:Account</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat surface is a two-dimensional continuant fiat boundary that is self-connected</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>A PersonState when they hold an Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000146</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>fiat surface</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#MoneyTransfer</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Money Transfer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:BusinessEvent | SubClassOf: ies:TradeEvent | SubClassOf: ies:transferValue only ies:AmountOfMoney</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat surface is a two-dimensional continuant fiat boundary that is self-connected</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>A BusinessEvent where an AmountOfMoney is moved from one FinancialAccount to another.
+Usually a Money Transfer event will involve two accounts but we might not know both, or it might be a cash transfer – in which case only one of the participants might be specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000146</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>fiat surface</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#ResponsibleActorState</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Responsible Actor State</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:ActorState | SubClassOf: ies:worksFor only ies:ResponsibleActor</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat surface is a two-dimensional continuant fiat boundary that is self-connected</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>A temporal state of a ResponsibleActor
+Note:  this is the superclass of ResponsibleActor (the whole life person or organisation) because the whole-life state is just a special case of a ResponsibleActorState. This pattern is true for all states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000146</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>fiat surface</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SubClassOf: ns1:BFO_0000140 | SubClassOf: ns1:BFO_0000178 only ns1:BFO_0000140</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>http://ies.data.gov.uk/ontology/ies4#RadioMast</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Radio Mast</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>R:only</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>SubClassOf: ies:Device | SubClassOf: ies:SystemState | SubClassOf: ies:radioCoverage only ies:RadioCoverageArea</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>(Elucidation) A fiat surface is a two-dimensional continuant fiat boundary that is self-connected</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>An Device that is placed in a Location to provide either a link from a wired to wireless connection, or to relay between two wireless endpoints.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
